--- a/Attendance/Absent_06-11-2025.xlsx
+++ b/Attendance/Absent_06-11-2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,66 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Parthiban P</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>06-11-2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VENKATANATHAN P R</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>06-11-2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
